--- a/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales sin gluten</t>
+          <t>Meses en la que empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,28</t>
+          <t>4,22; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 6,15</t>
+          <t>4,71; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,12</t>
+          <t>5,02; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,48</t>
+          <t>4,12; 5,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,14</t>
+          <t>4,79; 6,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,85</t>
+          <t>5,32; 6,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 5,22</t>
+          <t>4,25; 5,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,81</t>
+          <t>4,88; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 6,53</t>
+          <t>5,41; 6,58</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,14</t>
+          <t>4,18; 5,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,83</t>
+          <t>4,88; 5,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,91</t>
+          <t>5,02; 5,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 4,72</t>
+          <t>3,9; 4,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,98</t>
+          <t>4,96; 6,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,18</t>
+          <t>4,84; 6,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 4,73</t>
+          <t>4,15; 4,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,73</t>
+          <t>5,02; 5,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 5,85</t>
+          <t>5,06; 5,86</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,4</t>
+          <t>4,51; 5,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,81</t>
+          <t>4,55; 5,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,27</t>
+          <t>4,44; 6,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,06</t>
+          <t>3,64; 5,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,77</t>
+          <t>4,53; 5,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,73</t>
+          <t>4,32; 6,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,02</t>
+          <t>4,2; 5,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,5</t>
+          <t>4,66; 5,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,06</t>
+          <t>4,65; 6,08</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 4,55</t>
+          <t>3,69; 4,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 5,8</t>
+          <t>4,7; 5,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,09</t>
+          <t>5,54; 7,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,19</t>
+          <t>4,52; 6,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,1</t>
+          <t>4,4; 5,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,1</t>
+          <t>4,49; 6,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,13</t>
+          <t>4,23; 5,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 5,3</t>
+          <t>4,68; 5,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,6</t>
+          <t>5,26; 6,5</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 4,73</t>
+          <t>4,26; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,48</t>
+          <t>4,94; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,12</t>
+          <t>5,32; 6,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 4,99</t>
+          <t>4,32; 5,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,38</t>
+          <t>4,87; 5,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,92</t>
+          <t>5,13; 5,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 5,34</t>
+          <t>4,96; 5,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 5,85</t>
+          <t>5,31; 5,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,3</t>
+          <t>4,22; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,25</t>
+          <t>4,72; 6,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,03</t>
+          <t>5,1; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,52</t>
+          <t>4,17; 5,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,17</t>
+          <t>4,81; 6,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,7</t>
+          <t>5,3; 6,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 5,13</t>
+          <t>4,27; 5,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,83</t>
+          <t>4,88; 5,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,41; 6,58</t>
+          <t>5,36; 6,53</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,16</t>
+          <t>4,2; 5,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,74</t>
+          <t>4,92; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,9</t>
+          <t>5,07; 5,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,72</t>
+          <t>3,9; 4,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,03</t>
+          <t>4,92; 5,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,2</t>
+          <t>4,89; 6,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 4,76</t>
+          <t>4,16; 4,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,7</t>
+          <t>4,99; 5,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,86</t>
+          <t>5,05; 5,87</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 5,38</t>
+          <t>4,46; 5,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,78</t>
+          <t>4,6; 5,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,27</t>
+          <t>4,47; 6,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,07</t>
+          <t>3,6; 5,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,68</t>
+          <t>4,53; 5,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,83</t>
+          <t>4,38; 6,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,05</t>
+          <t>4,19; 5,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 5,42</t>
+          <t>4,65; 5,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,08</t>
+          <t>4,59; 5,99</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,52</t>
+          <t>3,68; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 5,79</t>
+          <t>4,74; 5,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,31</t>
+          <t>5,56; 7,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,13</t>
+          <t>4,51; 6,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,08</t>
+          <t>4,43; 5,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,13</t>
+          <t>4,48; 6,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,12</t>
+          <t>4,23; 5,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 5,31</t>
+          <t>4,69; 5,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,5</t>
+          <t>5,24; 6,51</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,26; 4,75</t>
+          <t>4,23; 4,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,46</t>
+          <t>4,92; 5,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,32; 6,14</t>
+          <t>5,35; 6,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,01</t>
+          <t>4,34; 5,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,37</t>
+          <t>4,86; 5,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 5,94</t>
+          <t>5,1; 5,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 5,35</t>
+          <t>4,95; 5,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">

--- a/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,31</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,26</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 5,22</t>
+          <t>4,12; 5,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,19</t>
+          <t>4,79; 6,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,03</t>
+          <t>5,36; 6,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,56</t>
+          <t>4,22; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,17</t>
+          <t>4,64; 6,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,81</t>
+          <t>5,04; 7,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 5,17</t>
+          <t>4,27; 5,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,85</t>
+          <t>4,87; 5,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,53</t>
+          <t>5,41; 6,53</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,35</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,35</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,61</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,26</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,42</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,28</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,14</t>
+          <t>3,93; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,75</t>
+          <t>4,94; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 5,93</t>
+          <t>4,86; 6,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 4,68</t>
+          <t>4,22; 5,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,91</t>
+          <t>4,93; 5,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,34</t>
+          <t>5,03; 5,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 4,78</t>
+          <t>4,14; 4,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 5,66</t>
+          <t>5,03; 5,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 5,87</t>
+          <t>5,07; 5,85</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,92</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,33</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,88</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,09</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,92</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,44</t>
+          <t>3,66; 5,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,7</t>
+          <t>4,53; 5,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,23</t>
+          <t>4,38; 6,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,06</t>
+          <t>4,48; 5,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,66</t>
+          <t>4,61; 5,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,67</t>
+          <t>4,53; 6,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,02</t>
+          <t>4,17; 5,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 5,49</t>
+          <t>4,7; 5,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,99</t>
+          <t>4,62; 6,06</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,07</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,75</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,15</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,51</t>
+          <t>4,49; 6,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 5,74</t>
+          <t>4,44; 5,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 7,19</t>
+          <t>4,49; 6,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,18</t>
+          <t>3,62; 4,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,12</t>
+          <t>4,74; 5,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,19</t>
+          <t>5,42; 7,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,21</t>
+          <t>4,24; 5,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 5,31</t>
+          <t>4,67; 5,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,51</t>
+          <t>5,26; 6,6</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,46</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,67</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 4,75</t>
+          <t>4,36; 4,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,47</t>
+          <t>4,87; 5,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,08</t>
+          <t>5,1; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,0</t>
+          <t>4,24; 4,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,37</t>
+          <t>4,92; 5,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,95</t>
+          <t>5,32; 6,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 5,33</t>
+          <t>4,97; 5,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 5,88</t>
+          <t>5,33; 5,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3001_MoAR-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer cereales sin gluten (tasa de respuesta: 64,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,71</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,66</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.705764715933192</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.305119886414179</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.92202614011742</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.609506302075481</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.260539400315857</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>5.803096644296208</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>4.663937365755826</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>5.285508935248156</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>5.882485536749593</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,12; 5,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4,79; 6,14</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,36; 6,85</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,22; 5,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,64; 6,15</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,04; 7,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,27; 5,22</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 5,81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 6,53</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>4.121705506559618</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>4.792853158806587</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5.355984238034342</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.223610007426879</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4.643025626287773</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>5.039756265675433</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.266354380476126</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>4.866640088379627</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5.407753102101871</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.47668293959909</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.136977620504128</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.848773673445402</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.284003827688719</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.149799206547637</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>7.123400075737297</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5.219478385501557</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>5.805414419145075</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6.534233064242134</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,28</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,61</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,42</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,42</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,93; 4,72</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,94; 5,98</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,86; 6,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,22; 5,14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,93; 5,83</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 5,91</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,14; 4,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 5,73</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,07; 5,85</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.275330773810203</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.345791924203656</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.346801686002772</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.611810326736629</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.262834907043998</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.422727797941728</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>4.420866717036098</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5.307523749298737</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.384076935612414</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,88</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,6</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3.930298533574553</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4.944236482931906</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4.860838366378191</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.221246744198091</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>4.934975553705481</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>5.028019802990031</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.142973383196294</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>5.030018914599509</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.071308701069166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,66; 5,06</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,53; 5,77</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,38; 6,73</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4,48; 5,4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,61; 5,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>4,53; 6,27</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,17; 5,02</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>4,7; 5,5</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>4,62; 6,06</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.724189741991106</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.976322037471322</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.178076916693594</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.138539329736248</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.825355432612688</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>5.911857466853218</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.734616545735496</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>5.729930837040442</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.851253029397799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,07</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,13</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,96</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5,76</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.319151569787449</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.92067198405944</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.327760622415124</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.884458523480119</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.067082623583087</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5.091712345579213</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>4.604578240319963</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4.995010977868226</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5.20897626686221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 6,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,44; 5,1</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 6,1</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3,62; 4,55</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4,74; 5,8</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,42; 7,09</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 5,13</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>4,67; 5,3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5,26; 6,6</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>3.655813948381864</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4.534662004901488</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>4.382640382210597</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>4.482068303216119</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>4.609878371919107</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>4.525298685242828</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4.166906136792509</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>4.701272149815648</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>4.620376478982108</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.056378537632014</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.770215888325114</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.726763424935814</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.404904100148075</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>5.808777083399702</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>6.269892102649231</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.015967328209472</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>5.495206727201194</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.056814623483641</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.068852943552419</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>4.754188560014068</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5.116398353524368</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.1108686202694</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>5.150464992495627</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>6.130465719723019</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>4.590271239104732</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>4.96218328375519</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>5.759866581887383</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4.491563343840274</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4.436780048974575</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>4.490990165594627</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>3.619293029842376</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>4.744144901306566</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5.423568164900724</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>4.23716972401194</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>4.67317602806295</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.263340667663578</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.194635869767929</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.103991040360637</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.103428796919323</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.551215226673098</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5.804756978704992</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.091930836086873</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>5.126841388923246</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>5.298224560354803</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6.595364668465766</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,62</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,18</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4,36; 4,99</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 5,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,1; 5,92</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 4,73</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,92; 5,48</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,32; 6,12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,36; 4,79</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 5,34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5,33; 5,85</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>4.623169441346724</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.084919452672568</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.45947786977918</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4.488866288940865</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.183113466281289</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5.668700994366628</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>4.560090218528237</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>5.132672542083224</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.56415128719219</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4.362319270880767</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>4.868761565682787</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>5.100970737069201</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4.243580099413991</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.917920296672051</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>5.318463095166805</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>4.363105510219998</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>4.972381548922428</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5.325066057559468</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.988537654462005</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.384132268340358</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.923873191702869</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.72680063168068</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.475785345562963</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>6.123467817202262</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>4.786656673208167</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>5.340168167740087</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.854590976547825</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
